--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N33_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>99.25363569770488</v>
+        <v>16.12871580087704</v>
       </c>
       <c r="D2" t="n">
-        <v>4.636853916760079</v>
+        <v>0.7534887614735128</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
